--- a/Untitled spreadsheet.xlsx
+++ b/Untitled spreadsheet.xlsx
@@ -326,7 +326,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AM54"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1" outlineLevelCol="0"/>
   <cols>
     <col width="13.38" customWidth="1" style="3" min="1" max="1"/>
     <col width="14.88" customWidth="1" style="3" min="13" max="13"/>
@@ -511,3984 +511,5133 @@
       <c r="AM1" s="1" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="0" t="inlineStr">
         <is>
           <t>HDFC Bank</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="0" t="inlineStr">
         <is>
           <t>All Miles Credit Card</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="0" t="inlineStr">
         <is>
           <t>e73bf938b396</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="0" t="inlineStr">
         <is>
           <t>credit</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="E2" s="0" t="inlineStr">
+        <is>
+          <t>Visa (est)</t>
+        </is>
+      </c>
+      <c r="F2" s="0" t="inlineStr">
+        <is>
+          <t>Premium Travel / Signature equivalent (est)</t>
+        </is>
+      </c>
+      <c r="G2" s="0" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="0" t="inlineStr">
         <is>
           <t>https://www.hdfcbank.com/credit-cards/all-miles-credit-card</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="0" t="inlineStr">
         <is>
           <t>2026-06-06T15:39:00.717498+00:00</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="K2" s="0" t="inlineStr">
+        <is>
+          <t>₹2,500 (est)</t>
+        </is>
+      </c>
+      <c r="L2" s="0" t="inlineStr">
+        <is>
+          <t>₹2,500 (est), waived on annual spends of ₹3,00,000 (est)</t>
+        </is>
+      </c>
+      <c r="M2" s="0" t="inlineStr">
+        <is>
+          <t>Upto ₹100 for ₹100-500 outstanding, ₹500 for ₹501-5000, ₹600 for ₹5001-10000, ₹800 for ₹10001-25000, ₹1000 for ₹25001-50000, ₹1300 for &gt;₹50000 (est)</t>
+        </is>
+      </c>
+      <c r="N2" s="0" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
       </c>
-      <c r="P2" s="1" t="n"/>
-      <c r="R2" t="inlineStr">
+      <c r="O2" s="0" t="inlineStr">
+        <is>
+          <t>₹99 + GST (est)</t>
+        </is>
+      </c>
+      <c r="P2" s="1" t="inlineStr">
+        <is>
+          <t>2.00% (est)</t>
+        </is>
+      </c>
+      <c r="R2" s="0" t="inlineStr">
         <is>
           <t>points</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S2" s="0" t="inlineStr">
         <is>
           <t>3X Reward Points for every ₹150 spent</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T2" s="0" t="inlineStr">
         <is>
           <t>hotel bookings, mobile recharge and shopping: 2X Reward Points</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="U2" s="0" t="inlineStr">
+        <is>
+          <t>Welcome bonus miles/points (est), Milestone bonus on achieving spending thresholds (est)</t>
+        </is>
+      </c>
+      <c r="V2" s="0" t="inlineStr">
         <is>
           <t>1% Fuel Surcharge waived off on fuel transactions</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="W2" s="0" t="inlineStr">
+        <is>
+          <t>4 complimentary visits per calendar year (est)</t>
+        </is>
+      </c>
+      <c r="X2" s="0" t="inlineStr">
+        <is>
+          <t>4 complimentary visits per calendar year via Priority Pass (est)</t>
+        </is>
+      </c>
+      <c r="Y2" s="0" t="inlineStr">
+        <is>
+          <t>Accelerated reward points on travel bookings (est), discounts on airline/hotel bookings (est)</t>
+        </is>
+      </c>
+      <c r="Z2" s="0" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="AB2" s="0" t="inlineStr">
+        <is>
+          <t>Salaried: ₹60,000 - ₹1,00,000 per month (est), Self-employed: ₹7.5 - ₹12 Lakhs ITR per annum (est)</t>
+        </is>
+      </c>
+      <c r="AC2" s="0" t="inlineStr">
+        <is>
+          <t>Salaried, Self-employed (est)</t>
+        </is>
+      </c>
+      <c r="AE2" s="0" t="inlineStr">
+        <is>
+          <t>Tier 1, Tier 2 (est)</t>
+        </is>
+      </c>
+      <c r="AF2" s="0" t="inlineStr">
+        <is>
+          <t>750+ (est)</t>
+        </is>
+      </c>
+      <c r="AG2" s="0" t="inlineStr">
+        <is>
+          <t>No (est)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="0" t="inlineStr">
         <is>
           <t>HDFC Bank</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="0" t="inlineStr">
         <is>
           <t>Bharat Credit Card</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="0" t="inlineStr">
         <is>
           <t>d1b238ef84f4</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="0" t="inlineStr">
         <is>
           <t>credit</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="0" t="inlineStr">
         <is>
           <t>RuPay</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="0" t="inlineStr">
         <is>
           <t>cashback</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="0" t="inlineStr">
         <is>
           <t>https://www.hdfcbank.com/credit-cards/bharat-credit-card</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="0" t="inlineStr">
         <is>
           <t>2026-06-06T15:39:41.866774+00:00</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" s="0" t="inlineStr">
         <is>
           <t>500</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Rs. 500</t>
+        </is>
+      </c>
+      <c r="R3" s="0" t="inlineStr">
         <is>
           <t>points/cashback</t>
         </is>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>1% (est)</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>Rs. 12,000 per month (est)</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Salaried &amp; Self-Employed</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>700+ (est)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="0" t="inlineStr">
         <is>
           <t>HDFC Bank</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="0" t="inlineStr">
         <is>
           <t>Diners Club Black Credit Card</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="0" t="inlineStr">
         <is>
           <t>a42e536328fd</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="0" t="inlineStr">
         <is>
           <t>credit</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="0" t="inlineStr">
         <is>
           <t>Diners Club</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="0" t="inlineStr">
         <is>
           <t>black</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="0" t="inlineStr">
         <is>
           <t>lifestyle</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="0" t="inlineStr">
         <is>
           <t>https://www.hdfcbank.com/credit-cards/diners-club-black-credit-card</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="0" t="inlineStr">
         <is>
           <t>2026-06-06T15:42:12.446199+00:00</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Rs. 10,000</t>
+        </is>
+      </c>
+      <c r="L4" s="0" t="inlineStr">
         <is>
           <t>10000</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P4" s="0" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="R4" s="0" t="inlineStr">
         <is>
           <t>points</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S4" s="0" t="inlineStr">
         <is>
           <t>5 Reward Points for every ₹150/- spent</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="Z4" s="0" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>Rs. 1.75 Lakhs per month (Salaried) or ITR &gt; Rs. 21 Lakhs per annum (Self-Employed)</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Salaried &amp; Self-Employed</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>750+ (est)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="0" t="inlineStr">
         <is>
           <t>HDFC Bank</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="0" t="inlineStr">
         <is>
           <t>Diners Club Black Metal Credit Card</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="0" t="inlineStr">
         <is>
           <t>bd68569cc050</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="0" t="inlineStr">
         <is>
           <t>credit</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="0" t="inlineStr">
         <is>
           <t>Diners Club</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="0" t="inlineStr">
         <is>
           <t>black metal edition</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="0" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="0" t="inlineStr">
         <is>
           <t>https://www.hdfcbank.com/credit-cards/diners-club-black-metal-edition-credit-card</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="0" t="inlineStr">
         <is>
           <t>2026-06-06T15:43:29.194071+00:00</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Rs. 10,000</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Rs. 10,000</t>
+        </is>
+      </c>
+      <c r="R5" s="0" t="inlineStr">
         <is>
           <t>points</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>3.33%</t>
+        </is>
+      </c>
+      <c r="Z5" s="0" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>Rs. 1.75 Lakhs per month (Salaried) or ITR &gt; Rs. 21 Lakhs per annum (Self-Employed)</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Salaried &amp; Self-Employed</t>
+        </is>
+      </c>
+      <c r="AD5" s="0" t="inlineStr">
         <is>
           <t>21 - 60</t>
         </is>
       </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>750+ (est)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="0" t="inlineStr">
         <is>
           <t>HDFC Bank</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="0" t="inlineStr">
         <is>
           <t>Diners Club Miles Credit Card</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="0" t="inlineStr">
         <is>
           <t>dd31edecf486</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="0" t="inlineStr">
         <is>
           <t>credit</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="0" t="inlineStr">
         <is>
           <t>Diners Club</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="0" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="0" t="inlineStr">
         <is>
           <t>https://www.hdfcbank.com/credit-cards/diners-club-miles-credit-card</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="0" t="inlineStr">
         <is>
           <t>2026-06-06T15:44:23.456247+00:00</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K6" s="0" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Rs. 1,000 (est)</t>
+        </is>
+      </c>
+      <c r="N6" s="0" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="R6" s="0" t="inlineStr">
         <is>
           <t>points/miles</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S6" s="0" t="inlineStr">
         <is>
           <t>4 Reward Points for every ₹200 spent</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="W6" s="0" t="inlineStr">
         <is>
           <t>6 complimentary lounge access annually</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Y6" s="0" t="inlineStr">
         <is>
           <t>Dining: 1400+ dining offers globally</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="Z6" s="0" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>Rs. 30,000 per month (est)</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Salaried &amp; Self-Employed</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>720+ (est)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="0" t="inlineStr">
         <is>
           <t>HDFC Bank</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="0" t="inlineStr">
         <is>
           <t>Diners Club Premium Credit Card</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="0" t="inlineStr">
         <is>
           <t>6ef672d2b5c9</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="0" t="inlineStr">
         <is>
           <t>credit</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="0" t="inlineStr">
         <is>
           <t>Diners Club</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="0" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="0" t="inlineStr">
         <is>
           <t>https://www.hdfcbank.com/credit-cards/diners-club-premium-credit-card</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="0" t="inlineStr">
         <is>
           <t>2026-06-06T15:45:24.793156+00:00</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K7" s="0" t="inlineStr">
         <is>
           <t>2500</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Rs. 2,500 (est)</t>
+        </is>
+      </c>
+      <c r="M7" s="0" t="inlineStr">
         <is>
           <t>3.6</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N7" s="0" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="P7" s="0" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="R7" s="0" t="inlineStr">
         <is>
           <t>points/miles</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="S7" s="0" t="inlineStr">
         <is>
           <t>4 Reward Points for every ₹200 spent</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" s="0" t="inlineStr">
         <is>
           <t>Welcome: 2,500 Reward points on card activation</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>Rs. 60,000 per month (est)</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Salaried &amp; Self-Employed</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>730+ (est)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="0" t="inlineStr">
         <is>
           <t>HDFC Bank</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="0" t="inlineStr">
         <is>
           <t>Diners Club Rewardz Credit Card</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="0" t="inlineStr">
         <is>
           <t>c4d1e4c94ce8</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="0" t="inlineStr">
         <is>
           <t>credit</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="0" t="inlineStr">
         <is>
           <t>Diners Club</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="0" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="0" t="inlineStr">
         <is>
           <t>https://www.hdfcbank.com/credit-cards/diners-club-rewardz-credit-card</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" s="0" t="inlineStr">
         <is>
           <t>2026-06-06T15:46:27.491653+00:00</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K8" s="0" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Rs. 1,000</t>
+        </is>
+      </c>
+      <c r="P8" s="0" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="R8" s="0" t="inlineStr">
         <is>
           <t>points</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S8" s="0" t="inlineStr">
         <is>
           <t>3 Reward Points for every ₹200 spent</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" s="0" t="inlineStr">
         <is>
           <t>Welcome: 1,000 Reward Points on card activation and renewal</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>Rs. 30,000 per month (est)</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Salaried &amp; Self-Employed</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>720+ (est)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="0" t="inlineStr">
         <is>
           <t>HDFC Bank</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="0" t="inlineStr">
         <is>
           <t>Diners Club Privilege Credit Card</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="0" t="inlineStr">
         <is>
           <t>970c0765f4bc</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="0" t="inlineStr">
         <is>
           <t>credit</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="0" t="inlineStr">
         <is>
           <t>Diners Club</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="0" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" s="0" t="inlineStr">
         <is>
           <t>https://www.hdfcbank.com/credit-cards/diners-privilege-credit-card</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" s="0" t="inlineStr">
         <is>
           <t>2026-06-06T15:47:56.654349+00:00</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Rs. 2,500</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Rs. 2,500</t>
+        </is>
+      </c>
+      <c r="P9" s="0" t="inlineStr">
         <is>
           <t>3.5%</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="R9" s="0" t="inlineStr">
         <is>
           <t>points</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S9" s="0" t="inlineStr">
         <is>
           <t>4 points per Rs.200 spent, 20 points on Swiggy and Zomato, up to 10X points via Smartbuy</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="T9" s="0" t="inlineStr">
         <is>
           <t>online food orders (Swiggy, Zomato): 5X Reward Points</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" s="0" t="inlineStr">
         <is>
           <t>Welcome: Rs.1500 worth vouchers from Marriott Experience, Barbeque Nation, Lakme Salon, O2 Spa, Decathlon, McDonalds or Dominos on quarterly milestone spend of Rs. 1.5 Lakhs | Milestone: Rs.1500 worth vouchers every quarter for spends of Rs. 1.5 Lakhs</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="W9" s="0" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="X9" s="0" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Y9" s="0" t="inlineStr">
         <is>
           <t>Movie: 'Buy One Get One' on weekend movie tickets, up to 2 free tickets every calendar month, up to a value of Rs. 250 per ticket via BookMyShow | Dining: Extra 10% off on Dineout bill on participating restaurants | Travel: Enjoy 2 domestic and 1 international lounge visits per calendar quarter by spending Rs. 60,000 in the previous quarter | Insurance: Air accident insurance cover worth $125,000, Emergency overseas hospitalization: $31,250, Travel Insurance Cover of up to $625 on baggage delay, Credit Liability Cover of up to ₹ 9 Lakh</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>Rs. 70,000 per month (Salaried) or ITR &gt; Rs. 8.4 Lakhs per annum (Self-Employed)</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Salaried &amp; Self-Employed</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>750+ (est)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="0" t="inlineStr">
         <is>
           <t>HDFC Bank</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="0" t="inlineStr">
         <is>
           <t>Doctor's Regalia Gold Credit Card</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="0" t="inlineStr">
         <is>
           <t>39e5c74c7d17</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="0" t="inlineStr">
         <is>
           <t>credit</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="0" t="inlineStr">
         <is>
           <t>Visa</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="0" t="inlineStr">
         <is>
           <t>gold</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" s="0" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H10" s="0" t="inlineStr">
         <is>
           <t>https://www.hdfcbank.com/credit-cards/doctors-regalia-credit-card</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I10" s="0" t="inlineStr">
         <is>
           <t>2026-06-06T15:49:27.030824+00:00</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Rs. 2,500</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Rs. 2,500</t>
+        </is>
+      </c>
+      <c r="P10" s="0" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="R10" s="0" t="inlineStr">
         <is>
           <t>points</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="S10" s="0" t="inlineStr">
         <is>
           <t>4 reward points on ₹ 150</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="W10" s="0" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="X10" s="0" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="Z10" s="0" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>Rs. 1,00,000 per month (est)</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Salaried &amp; Self-Employed Doctors</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>750+ (est)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="0" t="inlineStr">
         <is>
           <t>HDFC Bank</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="0" t="inlineStr">
         <is>
           <t>Doctor's Superia Credit Card</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="0" t="inlineStr">
         <is>
           <t>66e762f9b8c1</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="0" t="inlineStr">
         <is>
           <t>credit</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="0" t="inlineStr">
         <is>
           <t>Visa</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" s="0" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H11" s="0" t="inlineStr">
         <is>
           <t>https://www.hdfcbank.com/credit-cards/doctors-superia-credit-card</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I11" s="0" t="inlineStr">
         <is>
           <t>2026-06-06T15:50:27.695937+00:00</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K11" s="0" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Rs. 2,500 (est)</t>
+        </is>
+      </c>
+      <c r="R11" s="0" t="inlineStr">
         <is>
           <t>points</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S11" s="0" t="inlineStr">
         <is>
           <t>3 Reward Points for every ₹200 spent</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>Rs. 75,000 per month (est)</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Salaried &amp; Self-Employed Doctors</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>750+ (est)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="0" t="inlineStr">
         <is>
           <t>HDFC Bank</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="0" t="inlineStr">
         <is>
           <t>Flipkart Wholesale HDFC Bank Credit Card</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="0" t="inlineStr">
         <is>
           <t>fdd240005722</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="0" t="inlineStr">
         <is>
           <t>credit</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" s="0" t="inlineStr">
         <is>
           <t>cashback</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H12" s="0" t="inlineStr">
         <is>
           <t>https://www.hdfc.bank.in/credit-cards/flipkart-wholesale-credit-card</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I12" s="0" t="inlineStr">
         <is>
           <t>2026-06-06T15:51:28.908899+00:00</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="K12" s="0" t="inlineStr">
+        <is>
+          <t>500 (est)</t>
+        </is>
+      </c>
+      <c r="L12" s="0" t="inlineStr">
+        <is>
+          <t>500 (est)</t>
+        </is>
+      </c>
+      <c r="R12" s="0" t="inlineStr">
         <is>
           <t>cashback</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="S12" s="0" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" s="0" t="inlineStr">
         <is>
           <t>Welcome: ₹500 CashBack per transaction on first 3 purchases within 90 days of on-boarding</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="Z12" s="0" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
+      <c r="AB12" s="0" t="inlineStr">
+        <is>
+          <t>25000 (monthly) (est)</t>
+        </is>
+      </c>
+      <c r="AC12" s="0" t="inlineStr">
+        <is>
+          <t>Salaried, Self-employed</t>
+        </is>
+      </c>
+      <c r="AD12" s="0" t="inlineStr">
         <is>
           <t>21 years - 65 years</t>
         </is>
       </c>
+      <c r="AF12" s="0" t="inlineStr">
+        <is>
+          <t>700+</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="0" t="inlineStr">
         <is>
           <t>HDFC Bank</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="0" t="inlineStr">
         <is>
           <t>Freedom Credit Card</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="0" t="inlineStr">
         <is>
           <t>874c914415ec</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="0" t="inlineStr">
         <is>
           <t>credit</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" s="0" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H13" s="0" t="inlineStr">
         <is>
           <t>https://www.hdfc.bank.in/credit-cards/freedom-credit-card</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I13" s="0" t="inlineStr">
         <is>
           <t>2026-06-06T15:52:38.167786+00:00</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K13" s="0" t="inlineStr">
         <is>
           <t>500</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="L13" s="0" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="R13" s="0" t="inlineStr">
         <is>
           <t>points</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="S13" s="0" t="inlineStr">
         <is>
           <t>10X CashPoints on select merchants</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="T13" s="0" t="inlineStr">
         <is>
           <t>Big Basket, BookMyshow, OYO, Swiggy &amp; Uber: 10X CashPoints</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="U13" s="0" t="inlineStr">
         <is>
           <t>Welcome: 500 Reward Points on fee realisation | Milestone: Renewal membership fee waived off by spending ₹50,000 and above in an annual year</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="V13" s="0" t="inlineStr">
         <is>
           <t>1% fuel surcharge waiver at all fuel stations across India (on minimum transaction of ₹400 &amp; maximum transaction of ₹5,000. Maximum waiver of ₹250 per statement cycle)</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="Y13" s="0" t="inlineStr">
         <is>
           <t>Dining: 10% additional discount on Swiggy Dineout using coupon code HDFCCARDS | Travel: 10X CashPoints on Swiggy, Oyo, Uber, etc.</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="Z13" s="0" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
+      <c r="AB13" s="0" t="inlineStr">
         <is>
           <t>1200000000</t>
         </is>
       </c>
-      <c r="AD13" t="inlineStr">
+      <c r="AC13" s="0" t="inlineStr">
+        <is>
+          <t>Salaried, Self-employed</t>
+        </is>
+      </c>
+      <c r="AD13" s="0" t="inlineStr">
         <is>
           <t>21 years - 65 years for self-employed individuals</t>
         </is>
       </c>
+      <c r="AF13" s="0" t="inlineStr">
+        <is>
+          <t>700+</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="0" t="inlineStr">
         <is>
           <t>HDFC Bank</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="0" t="inlineStr">
         <is>
           <t>HDFC Bank UPI RuPay Credit Card</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="0" t="inlineStr">
         <is>
           <t>4e42098f353c</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="0" t="inlineStr">
         <is>
           <t>credit</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="0" t="inlineStr">
         <is>
           <t>RuPay</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G14" s="0" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H14" s="0" t="inlineStr">
         <is>
           <t>https://www.hdfcbank.com/personal-banking/credit-cards/hdfc-bank-upi-rupay-credit-card</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I14" s="0" t="inlineStr">
         <is>
           <t>2026-06-06T15:53:36.664265+00:00</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="K14" s="0" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="L14" s="0" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="R14" s="0" t="inlineStr">
         <is>
           <t>CashPoints</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="S14" s="0" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="T14" s="0" t="inlineStr">
         <is>
           <t>Groceries, Restaurant &amp; PayZapp transactions: 3%; Utility payments: 2%; Other spends: 1%</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="U14" s="0" t="inlineStr">
         <is>
           <t>Milestone: Renewal membership fee waived off by spending ₹25,000 and above in an annual year</t>
         </is>
       </c>
+      <c r="AB14" s="0" t="inlineStr">
+        <is>
+          <t>15000 (monthly) (est)</t>
+        </is>
+      </c>
+      <c r="AC14" s="0" t="inlineStr">
+        <is>
+          <t>Salaried, Self-employed</t>
+        </is>
+      </c>
+      <c r="AF14" s="0" t="inlineStr">
+        <is>
+          <t>680+ (est)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="0" t="inlineStr">
         <is>
           <t>HDFC Bank</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="0" t="inlineStr">
         <is>
           <t>Indian Oil HDFC Bank Credit Card</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="0" t="inlineStr">
         <is>
           <t>d3d104a575db</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="0" t="inlineStr">
         <is>
           <t>credit</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G15" s="0" t="inlineStr">
         <is>
           <t>fuel</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H15" s="0" t="inlineStr">
         <is>
           <t>https://www.hdfc.bank.in/credit-cards/indianoil-hdfc-bank-credit-card</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I15" s="0" t="inlineStr">
         <is>
           <t>2026-06-06T15:54:40.281248+00:00</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K15" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="L15" s="0" t="inlineStr">
         <is>
           <t>500</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="R15" s="0" t="inlineStr">
         <is>
           <t>Fuel Points</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="S15" s="0" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="T15" s="0" t="inlineStr">
         <is>
           <t>Groceries &amp; Bill Payments: 5%; Other Purchases (including UPI transactions): 1 Fuel Point for every ₹150 spent</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="U15" s="0" t="inlineStr">
         <is>
           <t>Welcome: INR 250 worth of voucher upon card activation and completion of at least one transaction within 37 days from card issuance date</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="V15" s="0" t="inlineStr">
         <is>
           <t>1% Fuel Surcharge waiver at all Indian fuel stations (min ₹400/transaction, max ₹250/cycle)</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
+      <c r="Z15" s="0" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
+      <c r="AB15" s="0" t="inlineStr">
         <is>
           <t>1200000000</t>
         </is>
       </c>
-      <c r="AD15" t="inlineStr">
+      <c r="AC15" s="0" t="inlineStr">
+        <is>
+          <t>Salaried, Self-employed</t>
+        </is>
+      </c>
+      <c r="AD15" s="0" t="inlineStr">
         <is>
           <t>Minimum 21 years - Maximum 65 years for self-employed individuals</t>
         </is>
       </c>
+      <c r="AF15" s="0" t="inlineStr">
+        <is>
+          <t>700+</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="0" t="inlineStr">
         <is>
           <t>HDFC Bank</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="0" t="inlineStr">
         <is>
           <t>Infinia Metal Credit Card</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="0" t="inlineStr">
         <is>
           <t>d872dd184bbf</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="0" t="inlineStr">
         <is>
           <t>credit</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="0" t="inlineStr">
         <is>
           <t>RuPay</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" s="0" t="inlineStr">
         <is>
           <t>metal</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G16" s="0" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H16" s="0" t="inlineStr">
         <is>
           <t>https://www.hdfcbank.com/credit-cards/infinia-credit-card</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I16" s="0" t="inlineStr">
         <is>
           <t>2026-06-06T15:55:47.475425+00:00</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="K16" s="0" t="inlineStr">
+        <is>
+          <t>12500</t>
+        </is>
+      </c>
+      <c r="L16" s="0" t="inlineStr">
+        <is>
+          <t>12500</t>
+        </is>
+      </c>
+      <c r="R16" s="0" t="inlineStr">
         <is>
           <t>points</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="S16" s="0" t="inlineStr">
         <is>
           <t>5 Reward Points for every ₹ 150 spent</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
+      <c r="Z16" s="0" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="AB16" s="0" t="inlineStr">
+        <is>
+          <t>350000</t>
+        </is>
+      </c>
+      <c r="AC16" s="0" t="inlineStr">
+        <is>
+          <t>Salaried, Self-employed</t>
+        </is>
+      </c>
+      <c r="AF16" s="0" t="inlineStr">
+        <is>
+          <t>750+</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="0" t="inlineStr">
         <is>
           <t>HDFC Bank</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="0" t="inlineStr">
         <is>
           <t>Diners Club Intermiles Credit Card</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="0" t="inlineStr">
         <is>
           <t>dc487f4588df</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="0" t="inlineStr">
         <is>
           <t>credit</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="0" t="inlineStr">
         <is>
           <t>Diners Club</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G17" s="0" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H17" s="0" t="inlineStr">
         <is>
           <t>https://www.hdfcbank.com/credit-cards/intermiles-diners-club-credit-card</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I17" s="0" t="inlineStr">
         <is>
           <t>2026-06-06T15:57:00.484364+00:00</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="K17" s="0" t="inlineStr">
+        <is>
+          <t>1000 (est)</t>
+        </is>
+      </c>
+      <c r="L17" s="0" t="inlineStr">
+        <is>
+          <t>1000 (est)</t>
+        </is>
+      </c>
+      <c r="P17" s="0" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="R17" s="0" t="inlineStr">
         <is>
           <t>InterMiles</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="S17" s="0" t="inlineStr">
         <is>
           <t>8 InterMiles on every ₹150 spent on retail purchases</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="U17" s="0" t="inlineStr">
         <is>
           <t>Welcome: 2,500 Reward points on card activation &amp; renewal</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
+      <c r="Z17" s="0" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
+      <c r="AB17" s="0" t="inlineStr">
         <is>
           <t>1440000</t>
         </is>
       </c>
-      <c r="AD17" t="inlineStr">
+      <c r="AC17" s="0" t="inlineStr">
+        <is>
+          <t>Salaried, Self-employed</t>
+        </is>
+      </c>
+      <c r="AD17" s="0" t="inlineStr">
         <is>
           <t>Min 21 years &amp; Max 60 years for salaried individuals; Min 21 years &amp; Max 65 years for self-employed individuals - ?</t>
         </is>
       </c>
+      <c r="AF17" s="0" t="inlineStr">
+        <is>
+          <t>700+</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="0" t="inlineStr">
         <is>
           <t>HDFC Bank</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="0" t="inlineStr">
         <is>
           <t>Intermiles Platinum Credit Card</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="0" t="inlineStr">
         <is>
           <t>de7a716eafa5</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="0" t="inlineStr">
         <is>
           <t>credit</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="0" t="inlineStr">
         <is>
           <t>Visa</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" s="0" t="inlineStr">
         <is>
           <t>platinum</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G18" s="0" t="inlineStr">
         <is>
           <t>travel</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H18" s="0" t="inlineStr">
         <is>
           <t>https://www.hdfcbank.com/credit-cards/intermiles-platinum-credit-card</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I18" s="0" t="inlineStr">
         <is>
           <t>2026-06-06T15:58:30.598130+00:00</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="K18" s="0" t="inlineStr">
+        <is>
+          <t>1000 (est)</t>
+        </is>
+      </c>
+      <c r="L18" s="0" t="inlineStr">
+        <is>
+          <t>1000 (est)</t>
+        </is>
+      </c>
+      <c r="R18" s="0" t="inlineStr">
         <is>
           <t>miles</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="S18" s="0" t="inlineStr">
         <is>
           <t>4 InterMiles for every ₹150 spent on retail purchases, 8 InterMiles for every ₹150 spent on flight tickets and hotels</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="W18" s="0" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="X18" s="0" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="AD18" t="inlineStr">
+      <c r="AB18" s="0" t="inlineStr">
+        <is>
+          <t>40000 (monthly) (est)</t>
+        </is>
+      </c>
+      <c r="AC18" s="0" t="inlineStr">
+        <is>
+          <t>Salaried, Self-employed</t>
+        </is>
+      </c>
+      <c r="AD18" s="0" t="inlineStr">
         <is>
           <t>21 - 60</t>
         </is>
       </c>
+      <c r="AF18" s="0" t="inlineStr">
+        <is>
+          <t>720+ (est)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="0" t="inlineStr">
         <is>
           <t>HDFC Bank</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="0" t="inlineStr">
         <is>
           <t>InterMiles Signature Credit Card</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="0" t="inlineStr">
         <is>
           <t>4c89dd0644cb</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="0" t="inlineStr">
         <is>
           <t>credit</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="0" t="inlineStr">
         <is>
           <t>Mastercard</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" s="0" t="inlineStr">
         <is>
           <t>signature</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G19" s="0" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H19" s="0" t="inlineStr">
         <is>
           <t>https://www.hdfcbank.com/credit-cards/intermiles-signature-credit-card</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I19" s="0" t="inlineStr">
         <is>
           <t>2026-06-06T15:59:42.203138+00:00</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="K19" s="0" t="inlineStr">
         <is>
           <t>2500</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="L19" s="0" t="inlineStr">
+        <is>
+          <t>2500 (est)</t>
+        </is>
+      </c>
+      <c r="R19" s="0" t="inlineStr">
         <is>
           <t>InterMiles</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="S19" s="0" t="inlineStr">
         <is>
           <t>6 InterMiles on every ₹150 spent on retail spends. 12 InterMiles on every ₹150 spent on flight tickets and hotel bookings.</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="V19" s="0" t="inlineStr">
         <is>
           <t>1% fuel surcharge waiver at all fuel stations across India on a minimum transaction of ₹400. Maximum waiver capped at ₹500 every billing cycle.</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="W19" s="0" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="Y19" s="0" t="inlineStr">
         <is>
           <t>Dining: Up to 20% discount on dining bills paid through Dineout Pay via your InterMiles Credit Card. Maximum discount per transaction capped at ₹1,000.</t>
         </is>
       </c>
+      <c r="AB19" s="0" t="inlineStr">
+        <is>
+          <t>75000 (monthly) (est)</t>
+        </is>
+      </c>
+      <c r="AC19" s="0" t="inlineStr">
+        <is>
+          <t>Salaried, Self-employed</t>
+        </is>
+      </c>
+      <c r="AF19" s="0" t="inlineStr">
+        <is>
+          <t>730+ (est)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="0" t="inlineStr">
         <is>
           <t>HDFC Bank</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="0" t="inlineStr">
         <is>
           <t>IRCTC HDFC Bank Credit Card</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="0" t="inlineStr">
         <is>
           <t>c53ef4fab498</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="0" t="inlineStr">
         <is>
           <t>credit</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="0" t="inlineStr">
         <is>
           <t>RuPay</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G20" s="0" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H20" s="0" t="inlineStr">
         <is>
           <t>https://www.hdfcbank.com/credit-cards/irctc-credit-card</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I20" s="0" t="inlineStr">
         <is>
           <t>2026-06-06T16:00:49.160721+00:00</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="K20" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="L20" s="0" t="inlineStr">
         <is>
           <t>500</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="R20" s="0" t="inlineStr">
         <is>
           <t>points</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="S20" s="0" t="inlineStr">
         <is>
           <t>5 Reward Points for every ₹100 spent via IRCTC, 1 Reward Point for every ₹100 on other spends</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="U20" s="0" t="inlineStr">
         <is>
           <t>Welcome: Gift voucher worth ₹500 upon activating the card</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="V20" s="0" t="inlineStr">
         <is>
           <t>1% fuel surcharge waiver at all fuel stations across India</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="W20" s="0" t="inlineStr">
         <is>
           <t>Complimentary access to select IRCTC lounges</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
+      <c r="Z20" s="0" t="inlineStr">
         <is>
           <t>Contactless payments</t>
         </is>
       </c>
-      <c r="AD20" t="inlineStr">
+      <c r="AB20" s="0" t="inlineStr">
+        <is>
+          <t>30000 (monthly) (est)</t>
+        </is>
+      </c>
+      <c r="AC20" s="0" t="inlineStr">
+        <is>
+          <t>Salaried, Self-employed</t>
+        </is>
+      </c>
+      <c r="AD20" s="0" t="inlineStr">
         <is>
           <t>21 years - 60 years for salaried individuals, 65 years for self-employed individuals</t>
         </is>
       </c>
+      <c r="AF20" s="0" t="inlineStr">
+        <is>
+          <t>700+</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="0" t="inlineStr">
         <is>
           <t>HDFC Bank</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="0" t="inlineStr">
         <is>
           <t>JetPrivilege Titanium Credit Card</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="0" t="inlineStr">
         <is>
           <t>bc72850ee336</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="0" t="inlineStr">
         <is>
           <t>credit</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" s="0" t="inlineStr">
         <is>
           <t>Visa</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" s="0" t="inlineStr">
         <is>
           <t>titanium</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G21" s="0" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H21" s="0" t="inlineStr">
         <is>
           <t>https://www.hdfcbank.com/credit-cards/jetprivilege-titanium-credit-card</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I21" s="0" t="inlineStr">
         <is>
           <t>2026-06-06T16:01:44.348259+00:00</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="K21" s="0" t="inlineStr">
         <is>
           <t>500</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="L21" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="R21" s="0" t="inlineStr">
         <is>
           <t>InterMiles</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="S21" s="0" t="inlineStr">
         <is>
           <t>2 InterMiles on every ₹150 spent on retail spends. 4 InterMiles on every ₹150 spent on every flight and hotel booked.</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="V21" s="0" t="inlineStr">
         <is>
           <t>Effective April 15, 2016, InterMiles will not be accrued on fuel transactions.</t>
         </is>
       </c>
+      <c r="AB21" s="0" t="inlineStr">
+        <is>
+          <t>30000 (monthly) (est)</t>
+        </is>
+      </c>
+      <c r="AC21" s="0" t="inlineStr">
+        <is>
+          <t>Salaried, Self-employed</t>
+        </is>
+      </c>
+      <c r="AF21" s="0" t="inlineStr">
+        <is>
+          <t>700+</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="0" t="inlineStr">
         <is>
           <t>HDFC Bank</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="0" t="inlineStr">
         <is>
           <t>Lifestyle Credit Card</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="0" t="inlineStr">
         <is>
           <t>8809727b0b93</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="0" t="inlineStr">
         <is>
           <t>credit</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" s="0" t="inlineStr">
         <is>
           <t>Visa</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" s="0" t="inlineStr">
         <is>
           <t>null</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G22" s="0" t="inlineStr">
         <is>
           <t>lifestyle</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H22" s="0" t="inlineStr">
         <is>
           <t>https://www.hdfcbank.com/credit-cards/lifestyle-credit-card</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I22" s="0" t="inlineStr">
         <is>
           <t>2026-06-06T16:02:53.412532+00:00</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="K22" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="L22" s="0" t="inlineStr">
         <is>
           <t>2500</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="M22" s="0" t="inlineStr">
         <is>
           <t>Applicable if not paid on time</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="N22" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="P22" s="0" t="inlineStr">
         <is>
           <t>null</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="R22" s="0" t="inlineStr">
         <is>
           <t>points/cashback/miles</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="S22" s="0" t="inlineStr">
         <is>
           <t>Varies by card variant (e.g., 5% Cashback on Amazon, Cult.fit, Bookmyshow &amp; More for Regalia Gold Credit Card)</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="T22" s="0" t="inlineStr">
         <is>
           <t>Shopping: 10x CashPoints on Amazon, Bigbasket, Swiggy &amp; More; Entertainment: 5x Rewards Points On Swiggy &amp; Zomato; Dining: Buy 1 Get 1 Free Via Bookmyshow; Travel: Club Vistara Silver Tier And Mmt Black Elite Membership</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="U22" s="0" t="inlineStr">
         <is>
           <t>Welcome: Vouchers, exclusive club memberships, etc. | Milestone: Complimentary Domestic Lounge Access at 1000+ Airports for Regalia Gold Credit Card</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="V22" s="0" t="inlineStr">
         <is>
           <t>Details vary by card variant</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
+      <c r="W22" s="0" t="inlineStr">
         <is>
           <t>1000+ Airports for Regalia Gold Credit Card</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="X22" s="0" t="inlineStr">
         <is>
           <t>null</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr">
+      <c r="Y22" s="0" t="inlineStr">
         <is>
           <t>Movie: Buy 1 Get 1 Free Via Bookmyshow | Dining: 5x Rewards Points On Swiggy &amp; Zomato | Travel: Club Vistara Silver Tier And Mmt Black Elite Membership, Vouchers Worth Up To ₹10,000 | Insurance: null</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
+      <c r="Z22" s="0" t="inlineStr">
         <is>
           <t>null</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
+      <c r="AB22" s="0" t="inlineStr">
         <is>
           <t>500000000000</t>
         </is>
       </c>
-      <c r="AD22" t="inlineStr">
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Salaried and Self-Employed</t>
+        </is>
+      </c>
+      <c r="AD22" s="0" t="inlineStr">
         <is>
           <t>21 - 65</t>
         </is>
       </c>
-      <c r="AF22" t="inlineStr">
+      <c r="AF22" s="0" t="inlineStr">
         <is>
           <t>null</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="0" t="inlineStr">
         <is>
           <t>HDFC Bank</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="0" t="inlineStr">
         <is>
           <t>Marriott Bonvoy® HDFC Bank Credit Card</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="0" t="inlineStr">
         <is>
           <t>c3a008aad04d</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="0" t="inlineStr">
         <is>
           <t>credit</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G23" s="0" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H23" s="0" t="inlineStr">
         <is>
           <t>https://www.hdfc.bank.in/credit-cards/marriott-bonvoy-credit-card</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I23" s="0" t="inlineStr">
         <is>
           <t>2026-06-06T16:03:58.922512+00:00</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Rs. 3000</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Rs. 3000</t>
+        </is>
+      </c>
+      <c r="R23" s="0" t="inlineStr">
         <is>
           <t>points</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="S23" s="0" t="inlineStr">
         <is>
           <t>8 points on every Rs.150 spent at hotels participating in Marriott Bonvoy</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="U23" s="0" t="inlineStr">
         <is>
           <t>Welcome: 1 Free Night Award (valued at 15,000 Marriott Bonvoy Points) and 10 Elite Night Credits*</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
+      <c r="W23" s="0" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="X23" s="0" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
+      <c r="Z23" s="0" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>Rs. 1,00,000 per month (salaried) / ITR &gt; Rs. 12 Lakhs per annum (self-employed)</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Salaried and Self-Employed</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>750 and above (est)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="0" t="inlineStr">
         <is>
           <t>HDFC Bank</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="0" t="inlineStr">
         <is>
           <t>Millennia Credit Card</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="0" t="inlineStr">
         <is>
           <t>74925b7710b4</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="0" t="inlineStr">
         <is>
           <t>credit</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E24" s="0" t="inlineStr">
         <is>
           <t>RuPay</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G24" s="0" t="inlineStr">
         <is>
           <t>cashback</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H24" s="0" t="inlineStr">
         <is>
           <t>https://www.hdfc.bank.in/credit-cards/millennia-credit-card</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I24" s="0" t="inlineStr">
         <is>
           <t>2026-06-06T16:05:01.071154+00:00</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Rs. 1000</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Rs. 1000</t>
+        </is>
+      </c>
+      <c r="R24" s="0" t="inlineStr">
         <is>
           <t>cashback</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="S24" s="0" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
+      <c r="Z24" s="0" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
+      <c r="AB24" s="0" t="inlineStr">
         <is>
           <t>3500000000</t>
         </is>
       </c>
-      <c r="AD24" t="inlineStr">
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Salaried and Self-Employed</t>
+        </is>
+      </c>
+      <c r="AD24" s="0" t="inlineStr">
         <is>
           <t>21 years - 40 years</t>
         </is>
       </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>750 and above (est)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="0" t="inlineStr">
         <is>
           <t>HDFC Bank</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="0" t="inlineStr">
         <is>
           <t>MoneyBack Credit Card</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="0" t="inlineStr">
         <is>
           <t>4b28f8ef3202</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" s="0" t="inlineStr">
         <is>
           <t>credit</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G25" s="0" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H25" s="0" t="inlineStr">
         <is>
           <t>https://www.hdfcbank.com/credit-cards/money-back-credit-card</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I25" s="0" t="inlineStr">
         <is>
           <t>2026-06-06T16:05:50.220946+00:00</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="K25" s="0" t="inlineStr">
         <is>
           <t>500</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="L25" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="R25" s="0" t="inlineStr">
         <is>
           <t>points/cashback</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="S25" s="0" t="inlineStr">
         <is>
           <t>2X Reward Points on every ₹200 spent online</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="U25" s="0" t="inlineStr">
         <is>
           <t>Welcome: 500 reward points upon card activation</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="V25" s="0" t="inlineStr">
         <is>
           <t>1% fuel surcharge waiver on ₹400-₹5,000 transaction amount. Maximum waiver is capped at ₹250 per statement cycle.</t>
         </is>
       </c>
-      <c r="Y25" t="inlineStr">
+      <c r="Y25" s="0" t="inlineStr">
         <is>
           <t>Dining: Dining privileges with Good Food Trail for max. 20% off on Swiggy Dineout</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
+      <c r="Z25" s="0" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>Rs. 25,000 per month (salaried) (est)</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Salaried and Self-Employed</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>700 and above (est)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="0" t="inlineStr">
         <is>
           <t>HDFC Bank</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="0" t="inlineStr">
         <is>
           <t>MoneyBack Plus Credit Card</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="0" t="inlineStr">
         <is>
           <t>e9782c09240b</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" s="0" t="inlineStr">
         <is>
           <t>credit</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G26" s="0" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H26" s="0" t="inlineStr">
         <is>
           <t>https://www.hdfcbank.com/credit-cards/moneyback-plus-credit-card</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I26" s="0" t="inlineStr">
         <is>
           <t>2026-06-06T16:06:57.410093+00:00</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="K26" s="0" t="inlineStr">
         <is>
           <t>500</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Rs. 500</t>
+        </is>
+      </c>
+      <c r="R26" s="0" t="inlineStr">
         <is>
           <t>points</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="S26" s="0" t="inlineStr">
         <is>
           <t>10X CashPoints (Upto 2.5% valueback)</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
+      <c r="Z26" s="0" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
+      <c r="AB26" s="0" t="inlineStr">
         <is>
           <t>2000000000</t>
         </is>
       </c>
-      <c r="AD26" t="inlineStr">
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Salaried and Self-Employed</t>
+        </is>
+      </c>
+      <c r="AD26" s="0" t="inlineStr">
         <is>
           <t>Minimum 21 years &amp; Maximum 60 years for Salaried and Minimum 21 years &amp; Maximum 65 years for Self-Employed - ?</t>
         </is>
       </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>700 and above (est)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="0" t="inlineStr">
         <is>
           <t>HDFC Bank</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="0" t="inlineStr">
         <is>
           <t>Paytm HDFC Bank Business Credit Card</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="0" t="inlineStr">
         <is>
           <t>4ca1923b0870</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" s="0" t="inlineStr">
         <is>
           <t>credit</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G27" s="0" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H27" s="0" t="inlineStr">
         <is>
           <t>https://www.hdfcbank.com/credit-cards/paytm-business-credit-card</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I27" s="0" t="inlineStr">
         <is>
           <t>2026-06-06T16:07:47.469724+00:00</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Rs. 500</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Rs. 500</t>
+        </is>
+      </c>
+      <c r="R27" s="0" t="inlineStr">
         <is>
           <t>CashPoints</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="S27" s="0" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="U27" s="0" t="inlineStr">
         <is>
           <t>Welcome: Paytm First Membership as a welcome benefit</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
+      <c r="Z27" s="0" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>ITR &gt; Rs. 6 Lakhs per annum (est)</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Self-Employed</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>720 and above (est)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="0" t="inlineStr">
         <is>
           <t>HDFC Bank</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="0" t="inlineStr">
         <is>
           <t>PhonePe HDFC Bank Ultimo Credit Card</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="0" t="inlineStr">
         <is>
           <t>c4e31b4f45a4</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" s="0" t="inlineStr">
         <is>
           <t>credit</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E28" s="0" t="inlineStr">
         <is>
           <t>RuPay</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F28" s="0" t="inlineStr">
         <is>
           <t>ultimo</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G28" s="0" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H28" s="0" t="inlineStr">
         <is>
           <t>https://www.hdfc.bank.in/credit-cards/phonepe-hdfc-bank-ultimo-credit-card</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I28" s="0" t="inlineStr">
         <is>
           <t>2026-06-06T16:08:55.087926+00:00</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="K28" s="0" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="L28" s="0" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="R28" s="0" t="inlineStr">
         <is>
           <t>points</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr">
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>1.33% (est)</t>
+        </is>
+      </c>
+      <c r="W28" s="0" t="inlineStr">
         <is>
           <t>8 per year, 2 per quarter</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
+      <c r="AB28" s="0" t="inlineStr">
         <is>
           <t>2500000000</t>
         </is>
       </c>
-      <c r="AD28" t="inlineStr">
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Salaried &amp; Self-Employed</t>
+        </is>
+      </c>
+      <c r="AD28" s="0" t="inlineStr">
         <is>
           <t>21 years - 60 years for salaried individuals and 65 years for self-employed</t>
         </is>
       </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>750 and above (est)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="0" t="inlineStr">
         <is>
           <t>HDFC Bank</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="0" t="inlineStr">
         <is>
           <t>PhonePe HDFC Bank Uno Credit Card</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="0" t="inlineStr">
         <is>
           <t>32e498162806</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" s="0" t="inlineStr">
         <is>
           <t>credit</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E29" s="0" t="inlineStr">
         <is>
           <t>RuPay</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F29" s="0" t="inlineStr">
         <is>
           <t>null</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G29" s="0" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H29" s="0" t="inlineStr">
         <is>
           <t>https://www.hdfcbank.com/credit-cards/phonepe-hdfc-bank-uno-credit-card</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="I29" s="0" t="inlineStr">
         <is>
           <t>2026-06-06T16:09:58.781102+00:00</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="K29" s="0" t="inlineStr">
         <is>
           <t>499</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="L29" s="0" t="inlineStr">
         <is>
           <t>499</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="M29" s="0" t="inlineStr">
         <is>
           <t>null</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="N29" s="0" t="inlineStr">
         <is>
           <t>null</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="P29" s="0" t="inlineStr">
         <is>
           <t>null</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="R29" s="0" t="inlineStr">
         <is>
           <t>points</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr">
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>0.67% (est)</t>
+        </is>
+      </c>
+      <c r="W29" s="0" t="inlineStr">
         <is>
           <t>null</t>
         </is>
       </c>
-      <c r="Y29" t="inlineStr">
+      <c r="Y29" s="0" t="inlineStr">
         <is>
           <t>Movie: null | Dining: null | Travel: null | Insurance: null</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
+      <c r="Z29" s="0" t="inlineStr">
         <is>
           <t>null</t>
         </is>
       </c>
-      <c r="AD29" t="inlineStr">
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>₹25,000 per month (est)</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Salaried &amp; Self-Employed</t>
+        </is>
+      </c>
+      <c r="AD29" s="0" t="inlineStr">
         <is>
           <t>21 years - 60 years for salaried, 65 years for self-employed</t>
         </is>
       </c>
-      <c r="AF29" t="inlineStr">
+      <c r="AF29" s="0" t="inlineStr">
         <is>
           <t>null</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="0" t="inlineStr">
         <is>
           <t>HDFC Bank</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="0" t="inlineStr">
         <is>
           <t>PhonePe HDFC Bank Credit Card</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="0" t="inlineStr">
         <is>
           <t>75cbd9980051</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D30" s="0" t="inlineStr">
         <is>
           <t>credit</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E30" s="0" t="inlineStr">
         <is>
           <t>RuPay</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G30" s="0" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H30" s="0" t="inlineStr">
         <is>
           <t>https://www.phonepe.com/credit-cards/phonepe-hdfc-credit-card</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="I30" s="0" t="inlineStr">
         <is>
           <t>2026-06-06T16:10:56.687259+00:00</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="K30" s="0" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>₹500 (est)</t>
+        </is>
+      </c>
+      <c r="R30" s="0" t="inlineStr">
         <is>
           <t>points</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="S30" s="0" t="inlineStr">
         <is>
           <t>1 Reward Point = ₹1</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="T30" s="0" t="inlineStr">
         <is>
           <t>Recharge, Bill Payments, Flight Booking, Hotel: 10% Reward Points; Flipkart, Amazon, Swiggy, Zomato, Uber, Myntra &amp; AJIO: 5% Reward Points; Scan and Pay payments through any UPI app: 1% Reward Points</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="U30" s="0" t="inlineStr">
         <is>
           <t>Welcome: Get cashback worth ₹499 on first UPI payment on PhonePe via this card*</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
+      <c r="V30" s="0" t="inlineStr">
         <is>
           <t>waiver on fuel surcharge worry-free fuel spends</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr">
+      <c r="W30" s="0" t="inlineStr">
         <is>
           <t>Complimentary Airport Lounge Access within India per year</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>₹20,000 per month (est)</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Salaried &amp; Self-Employed</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>21 - 65 Years (est)</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>700 and above (est)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="0" t="inlineStr">
         <is>
           <t>HDFC Bank</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="0" t="inlineStr">
         <is>
           <t>PIXEL Go Credit Card</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="0" t="inlineStr">
         <is>
           <t>671cb7915b57</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D31" s="0" t="inlineStr">
         <is>
           <t>credit</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E31" s="0" t="inlineStr">
         <is>
           <t>Visa</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G31" s="0" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H31" s="0" t="inlineStr">
         <is>
           <t>https://www.hdfc.bank.in/credit-cards/pixel-go-credit-card</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I31" s="0" t="inlineStr">
         <is>
           <t>2026-06-06T16:11:51.205716+00:00</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="K31" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>₹500 (est)</t>
+        </is>
+      </c>
+      <c r="R31" s="0" t="inlineStr">
         <is>
           <t>cashback/points</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="S31" s="0" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
+      <c r="Z31" s="0" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
+      <c r="AB31" s="0" t="inlineStr">
         <is>
           <t>12000</t>
         </is>
       </c>
-      <c r="AD31" t="inlineStr">
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Salaried &amp; Self-Employed</t>
+        </is>
+      </c>
+      <c r="AD31" s="0" t="inlineStr">
         <is>
           <t>21 - 65 (Self-Employed)</t>
         </is>
       </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>720 and above (est)</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="0" t="inlineStr">
         <is>
           <t>HDFC Bank</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="0" t="inlineStr">
         <is>
           <t>PIXEL Play Credit Card</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="0" t="inlineStr">
         <is>
           <t>2ca29439dfd1</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D32" s="0" t="inlineStr">
         <is>
           <t>credit</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E32" s="0" t="inlineStr">
         <is>
           <t>Visa</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G32" s="0" t="inlineStr">
         <is>
           <t>cashback</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H32" s="0" t="inlineStr">
         <is>
           <t>https://www.hdfcbank.com/credit-cards/pixel-play-credit-card</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="I32" s="0" t="inlineStr">
         <is>
           <t>2026-06-06T16:12:49.266116+00:00</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="K32" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr">
+      <c r="L32" s="0" t="inlineStr">
+        <is>
+          <t>₹250 + applicable taxes (waived on spends of ₹25,000 &amp; above in a year)</t>
+        </is>
+      </c>
+      <c r="R32" s="0" t="inlineStr">
         <is>
           <t>CashBack</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="S32" s="0" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
+      <c r="Z32" s="0" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
+      <c r="AB32" s="0" t="inlineStr">
         <is>
           <t>25000</t>
         </is>
       </c>
-      <c r="AD32" t="inlineStr">
+      <c r="AC32" s="0" t="inlineStr">
+        <is>
+          <t>Salaried, Self-Employed</t>
+        </is>
+      </c>
+      <c r="AD32" s="0" t="inlineStr">
         <is>
           <t>21 years - 60 years for Salaried and 65 years for Self-Employed</t>
         </is>
       </c>
+      <c r="AF32" s="0" t="inlineStr">
+        <is>
+          <t>700+ (est)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="0" t="inlineStr">
         <is>
           <t>HDFC Bank</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="0" t="inlineStr">
         <is>
           <t>Platinum Edge Credit Card</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="0" t="inlineStr">
         <is>
           <t>b5dc65534a64</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D33" s="0" t="inlineStr">
         <is>
           <t>credit</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E33" s="0" t="inlineStr">
         <is>
           <t>Visa</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F33" s="0" t="inlineStr">
         <is>
           <t>platinum</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G33" s="0" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H33" s="0" t="inlineStr">
         <is>
           <t>https://www.hdfcbank.com/credit-cards/platinum-edge-credit-card</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I33" s="0" t="inlineStr">
         <is>
           <t>2026-06-06T16:13:37.350536+00:00</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="K33" s="0" t="inlineStr">
+        <is>
+          <t>₹250 + applicable taxes</t>
+        </is>
+      </c>
+      <c r="L33" s="0" t="inlineStr">
+        <is>
+          <t>₹250 + applicable taxes (waived on spends of ₹50,000 &amp; above in a year)</t>
+        </is>
+      </c>
+      <c r="N33" s="0" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr">
+      <c r="R33" s="0" t="inlineStr">
         <is>
           <t>points/cashback</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
+      <c r="S33" s="0" t="inlineStr">
         <is>
           <t>2 Reward Points for every ₹200 spent</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
+      <c r="Z33" s="0" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="AB33" s="0" t="inlineStr">
+        <is>
+          <t>₹25,000 per month (Salaried), ₹6 Lakhs ITR per annum (Self-employed) (est)</t>
+        </is>
+      </c>
+      <c r="AC33" s="0" t="inlineStr">
+        <is>
+          <t>Salaried, Self-Employed</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>21 - 65 Years</t>
+        </is>
+      </c>
+      <c r="AF33" s="0" t="inlineStr">
+        <is>
+          <t>700+ (est)</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="0" t="inlineStr">
         <is>
           <t>HDFC Bank</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="0" t="inlineStr">
         <is>
           <t>Platinum Plus Credit Card</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="0" t="inlineStr">
         <is>
           <t>5b60dad76039</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D34" s="0" t="inlineStr">
         <is>
           <t>credit</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F34" s="0" t="inlineStr">
         <is>
           <t>platinum</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G34" s="0" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H34" s="0" t="inlineStr">
         <is>
           <t>https://www.hdfcbank.com/credit-cards/platinum-plus-credit-card</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="I34" s="0" t="inlineStr">
         <is>
           <t>2026-06-06T16:14:22.317173+00:00</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="K34" s="0" t="inlineStr">
+        <is>
+          <t>₹250 + applicable taxes</t>
+        </is>
+      </c>
+      <c r="L34" s="0" t="inlineStr">
+        <is>
+          <t>₹250 + applicable taxes (waived on spends of ₹50,000 &amp; above in a year)</t>
+        </is>
+      </c>
+      <c r="N34" s="0" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr">
+      <c r="R34" s="0" t="inlineStr">
         <is>
           <t>points</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
+      <c r="S34" s="0" t="inlineStr">
         <is>
           <t>4 Reward Points for every ₹ 200 spent</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr">
+      <c r="T34" s="0" t="inlineStr">
         <is>
           <t>Milestone Benefits: 50% more Reward Points on every ₹ 200 spent after crossing spends of ₹50,000 every month</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr">
+      <c r="U34" s="0" t="inlineStr">
         <is>
           <t>Milestone: 50% more Reward Points on every ₹ 200 spent after crossing spends of ₹50,000 every month</t>
         </is>
       </c>
+      <c r="AB34" s="0" t="inlineStr">
+        <is>
+          <t>₹25,000 per month (Salaried), ₹6 Lakhs ITR per annum (Self-employed) (est)</t>
+        </is>
+      </c>
+      <c r="AC34" s="0" t="inlineStr">
+        <is>
+          <t>Salaried, Self-Employed</t>
+        </is>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>21 - 65 Years</t>
+        </is>
+      </c>
+      <c r="AF34" s="0" t="inlineStr">
+        <is>
+          <t>700+ (est)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="0" t="inlineStr">
         <is>
           <t>HDFC Bank</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="0" t="inlineStr">
         <is>
           <t>Regalia Activ Credit Card</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="0" t="inlineStr">
         <is>
           <t>a9d730dc6eb8</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D35" s="0" t="inlineStr">
         <is>
           <t>credit</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E35" s="0" t="inlineStr">
         <is>
           <t>RuPay</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G35" s="0" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="H35" s="0" t="inlineStr">
         <is>
           <t>https://www.hdfcbank.com/credit-cards/regalia-activ-credit-card</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="I35" s="0" t="inlineStr">
         <is>
           <t>2026-06-06T16:15:27.220645+00:00</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="K35" s="0" t="inlineStr">
         <is>
           <t>2500</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="L35" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr">
+      <c r="R35" s="0" t="inlineStr">
         <is>
           <t>points</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
+      <c r="S35" s="0" t="inlineStr">
         <is>
           <t>4 Reward Points for every ₹200 spent (On all eligible retails spends.)</t>
         </is>
       </c>
-      <c r="V35" t="inlineStr">
+      <c r="V35" s="0" t="inlineStr">
         <is>
           <t>1% fuel surcharge waiver at all fuel stations across India (on minimum transaction of ₹400 and maximum transaction of ₹5,000).</t>
         </is>
       </c>
-      <c r="W35" t="inlineStr">
+      <c r="W35" s="0" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
+      <c r="X35" s="0" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
+      <c r="Z35" s="0" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
+      <c r="AB35" s="0" t="inlineStr">
+        <is>
+          <t>₹70,000 per month (Salaried), ₹8.4 Lakhs ITR per annum (Self-employed) (est)</t>
+        </is>
+      </c>
+      <c r="AC35" s="0" t="inlineStr">
+        <is>
+          <t>Salaried, Self-Employed</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>21 - 65 Years (est)</t>
+        </is>
+      </c>
+      <c r="AF35" s="0" t="inlineStr">
+        <is>
+          <t>750+ (est)</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="0" t="inlineStr">
         <is>
           <t>HDFC Bank</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="0" t="inlineStr">
         <is>
           <t>Regalia Credit Card</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="0" t="inlineStr">
         <is>
           <t>e0de31650d42</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D36" s="0" t="inlineStr">
         <is>
           <t>credit</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E36" s="0" t="inlineStr">
         <is>
           <t>RuPay</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F36" s="0" t="inlineStr">
         <is>
           <t>gold</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G36" s="0" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="H36" s="0" t="inlineStr">
         <is>
           <t>https://www.hdfcbank.com/credit-cards/regalia-credit-card</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="I36" s="0" t="inlineStr">
         <is>
           <t>2026-06-06T16:16:31.238076+00:00</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="K36" s="0" t="inlineStr">
         <is>
           <t>2500</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr">
+      <c r="L36" s="0" t="inlineStr">
+        <is>
+          <t>₹2,500 + applicable taxes (waived on spends of ₹3 Lakhs &amp; above in a year)</t>
+        </is>
+      </c>
+      <c r="R36" s="0" t="inlineStr">
         <is>
           <t>points</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr">
+      <c r="S36" s="0" t="inlineStr">
         <is>
           <t>4 Reward Points on every ₹200 spent</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr">
+      <c r="U36" s="0" t="inlineStr">
         <is>
           <t>Welcome: Welcome benefit of 2500 reward points</t>
         </is>
       </c>
+      <c r="AB36" s="0" t="inlineStr">
+        <is>
+          <t>₹1,00,000 per month (Salaried), ₹12 Lakhs ITR per annum (Self-employed)</t>
+        </is>
+      </c>
+      <c r="AC36" s="0" t="inlineStr">
+        <is>
+          <t>Salaried, Self-Employed</t>
+        </is>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>21 - 65 Years</t>
+        </is>
+      </c>
+      <c r="AF36" s="0" t="inlineStr">
+        <is>
+          <t>750+</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="0" t="inlineStr">
         <is>
           <t>HDFC Bank</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="0" t="inlineStr">
         <is>
           <t>Regalia Gold Credit Card</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="0" t="inlineStr">
         <is>
           <t>5991b739a34a</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D37" s="0" t="inlineStr">
         <is>
           <t>credit</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E37" s="0" t="inlineStr">
         <is>
           <t>RuPay</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F37" s="0" t="inlineStr">
         <is>
           <t>gold</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G37" s="0" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="H37" s="0" t="inlineStr">
         <is>
           <t>https://www.hdfcbank.com/credit-cards/regalia-first-credit-card</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="I37" s="0" t="inlineStr">
         <is>
           <t>2026-06-06T16:17:38.022192+00:00</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="K37" s="0" t="inlineStr">
+        <is>
+          <t>₹2,500 + applicable taxes</t>
+        </is>
+      </c>
+      <c r="L37" s="0" t="inlineStr">
+        <is>
+          <t>₹2,500 + applicable taxes (waived on spends of ₹4 Lakhs &amp; above in a year)</t>
+        </is>
+      </c>
+      <c r="P37" s="0" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr">
+      <c r="R37" s="0" t="inlineStr">
         <is>
           <t>points</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr">
+      <c r="S37" s="0" t="inlineStr">
         <is>
           <t>4 Reward Points on every ₹150 spent</t>
         </is>
       </c>
+      <c r="AB37" s="0" t="inlineStr">
+        <is>
+          <t>₹1,00,000 per month (Salaried), ₹12 Lakhs ITR per annum (Self-employed)</t>
+        </is>
+      </c>
+      <c r="AC37" s="0" t="inlineStr">
+        <is>
+          <t>Salaried, Self-Employed</t>
+        </is>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>21 - 65 Years</t>
+        </is>
+      </c>
+      <c r="AF37" s="0" t="inlineStr">
+        <is>
+          <t>750+</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="0" t="inlineStr">
         <is>
           <t>HDFC Bank</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="0" t="inlineStr">
         <is>
           <t>Regalia Gold Credit Card</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="0" t="inlineStr">
         <is>
           <t>5991b739a34a</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D38" s="0" t="inlineStr">
         <is>
           <t>credit</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F38" s="0" t="inlineStr">
         <is>
           <t>gold</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G38" s="0" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="H38" s="0" t="inlineStr">
         <is>
           <t>https://www.hdfc.bank.in/credit-cards/regalia-gold-credit-card</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="I38" s="0" t="inlineStr">
         <is>
           <t>2026-06-06T16:18:41.599989+00:00</t>
         </is>
       </c>
-      <c r="R38" t="inlineStr">
+      <c r="K38" s="0" t="inlineStr">
+        <is>
+          <t>₹2,500 + applicable taxes</t>
+        </is>
+      </c>
+      <c r="L38" s="0" t="inlineStr">
+        <is>
+          <t>₹2,500 + applicable taxes (waived on spends of ₹4 Lakhs &amp; above in a year)</t>
+        </is>
+      </c>
+      <c r="R38" s="0" t="inlineStr">
         <is>
           <t>points</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr">
+      <c r="S38" s="0" t="inlineStr">
         <is>
           <t>5X Reward Points on select brands, 5 Reward Points on every Rs. 200 spent (On retail spends)</t>
         </is>
       </c>
-      <c r="W38" t="inlineStr">
+      <c r="W38" s="0" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
+      <c r="X38" s="0" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
+      <c r="AB38" s="0" t="inlineStr">
+        <is>
+          <t>₹1,00,000 per month (Salaried), ₹12 Lakhs ITR per annum (Self-employed)</t>
+        </is>
+      </c>
+      <c r="AC38" s="0" t="inlineStr">
+        <is>
+          <t>Salaried, Self-Employed</t>
+        </is>
+      </c>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>21 - 65 Years</t>
+        </is>
+      </c>
+      <c r="AF38" s="0" t="inlineStr">
+        <is>
+          <t>750+</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="0" t="inlineStr">
         <is>
           <t>HDFC Bank</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="0" t="inlineStr">
         <is>
           <t>null</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="0" t="inlineStr">
         <is>
           <t>84024fc678d6</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D39" s="0" t="inlineStr">
         <is>
           <t>credit</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E39" s="0" t="inlineStr">
         <is>
           <t>Diners Club</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F39" s="0" t="inlineStr">
         <is>
           <t>black metal edition</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G39" s="0" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="H39" s="0" t="inlineStr">
         <is>
           <t>https://www.hdfcbank.com/credit-cards/rewards-credit-card</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="I39" s="0" t="inlineStr">
         <is>
           <t>2026-06-06T16:21:04.192519+00:00</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="K39" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="L39" s="0" t="inlineStr">
         <is>
           <t>10000</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="M39" s="0" t="inlineStr">
         <is>
           <t>null</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="N39" s="0" t="inlineStr">
         <is>
           <t>null</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
+      <c r="P39" s="0" t="inlineStr">
         <is>
           <t>null</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr">
+      <c r="R39" s="0" t="inlineStr">
         <is>
           <t>points</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr">
+      <c r="S39" s="0" t="inlineStr">
         <is>
           <t>null</t>
         </is>
       </c>
-      <c r="T39" t="inlineStr">
+      <c r="T39" s="0" t="inlineStr">
         <is>
           <t>Dining &amp; SmartBuy: Bonus Reward Points</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr">
+      <c r="U39" s="0" t="inlineStr">
         <is>
           <t>Welcome: 10,000 Bonus Reward Points on spends of ₹4 lakh every calendar quarter.</t>
         </is>
       </c>
-      <c r="V39" t="inlineStr">
+      <c r="V39" s="0" t="inlineStr">
         <is>
           <t>null</t>
         </is>
       </c>
-      <c r="W39" t="inlineStr">
+      <c r="W39" s="0" t="inlineStr">
         <is>
           <t>null</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
+      <c r="X39" s="0" t="inlineStr">
         <is>
           <t>null</t>
         </is>
       </c>
-      <c r="Y39" t="inlineStr">
+      <c r="Y39" s="0" t="inlineStr">
         <is>
           <t>Movie: null | Dining: null | Travel: Offers On Hotel &amp; Flight Bookings, 24x7 Concierge Service, Exclusive Gifts | Insurance: null</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
+      <c r="Z39" s="0" t="inlineStr">
         <is>
           <t>null</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
+      <c r="AB39" s="0" t="inlineStr">
         <is>
           <t>100000</t>
         </is>
       </c>
-      <c r="AD39" t="inlineStr">
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Salaried and Self-Employed (est)</t>
+        </is>
+      </c>
+      <c r="AD39" s="0" t="inlineStr">
         <is>
           <t>21 - null</t>
         </is>
       </c>
-      <c r="AF39" t="inlineStr">
+      <c r="AF39" s="0" t="inlineStr">
         <is>
           <t>null</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="0" t="inlineStr">
         <is>
           <t>HDFC Bank</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="0" t="inlineStr">
         <is>
           <t>RuPay Credit Card</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="0" t="inlineStr">
         <is>
           <t>f7441c1f7791</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D40" s="0" t="inlineStr">
         <is>
           <t>credit</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E40" s="0" t="inlineStr">
         <is>
           <t>RuPay</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G40" s="0" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="H40" s="0" t="inlineStr">
         <is>
           <t>https://www.hdfcbank.com/credit-cards/rupay-credit-card</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="I40" s="0" t="inlineStr">
         <is>
           <t>2026-06-06T16:21:54.151495+00:00</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr">
+      <c r="K40" s="0" t="inlineStr">
+        <is>
+          <t>₹250 + applicable taxes (est, for entry-level variant)</t>
+        </is>
+      </c>
+      <c r="L40" s="0" t="inlineStr">
+        <is>
+          <t>₹250 + applicable taxes (est, for entry-level variant)</t>
+        </is>
+      </c>
+      <c r="R40" s="0" t="inlineStr">
         <is>
           <t>points</t>
         </is>
       </c>
-      <c r="T40" t="inlineStr">
+      <c r="S40" s="0" t="inlineStr">
+        <is>
+          <t>0.5% - 0.75% (est)</t>
+        </is>
+      </c>
+      <c r="T40" s="0" t="inlineStr">
         <is>
           <t>Dining &amp; Entertainment: 5%; BookMyShow &amp; Zomato, Travel Category: 5%; MakeMyTrip &amp; Uber, Grocery Category: 5%; Blinkit &amp; Reliance Smart Bazaar, Electronics Category: 5%; Croma &amp; Reliance Digital, Fashion Category: 5%; Nykaa &amp; Myntra: 5%; Amazon or Flipkart or PayZapp: 3%; All spends*: 1%; UPI Spends (Applicable only on PIXEL RuPay Credit Card holders): 1%</t>
         </is>
       </c>
+      <c r="AB40" s="0" t="inlineStr">
+        <is>
+          <t>₹25,000 per month (Salaried), ₹6 Lakhs ITR per annum (Self-employed) (est)</t>
+        </is>
+      </c>
+      <c r="AC40" s="0" t="inlineStr">
+        <is>
+          <t>Salaried, Self-Employed</t>
+        </is>
+      </c>
+      <c r="AF40" s="0" t="inlineStr">
+        <is>
+          <t>700+ (est)</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="0" t="inlineStr">
         <is>
           <t>HDFC Bank</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="0" t="inlineStr">
         <is>
           <t>Shoppers Stop BLACK Credit Card</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="0" t="inlineStr">
         <is>
           <t>2a4d581aef47</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D41" s="0" t="inlineStr">
         <is>
           <t>credit</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E41" s="0" t="inlineStr">
         <is>
           <t>Visa</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F41" s="0" t="inlineStr">
         <is>
           <t>black</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G41" s="0" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="H41" s="0" t="inlineStr">
         <is>
           <t>https://www.hdfcbank.com/credit-cards/shoppers-stop-black-credit-card</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="I41" s="0" t="inlineStr">
         <is>
           <t>2026-06-06T16:22:46.556928+00:00</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr">
+      <c r="K41" s="0" t="inlineStr">
+        <is>
+          <t>₹2,500 + applicable taxes</t>
+        </is>
+      </c>
+      <c r="L41" s="0" t="inlineStr">
+        <is>
+          <t>₹2,500 + applicable taxes (waived on spends of ₹3 Lakhs &amp; above in a year)</t>
+        </is>
+      </c>
+      <c r="R41" s="0" t="inlineStr">
         <is>
           <t>points</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr">
+      <c r="S41" s="0" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
       </c>
-      <c r="U41" t="inlineStr">
+      <c r="U41" s="0" t="inlineStr">
         <is>
           <t>Welcome: Welcome Voucher Worth ₹1,500</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr">
+      <c r="V41" s="0" t="inlineStr">
         <is>
           <t>1% fuel surcharge waiver</t>
         </is>
       </c>
-      <c r="W41" t="inlineStr">
+      <c r="W41" s="0" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
+      <c r="X41" s="0" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
+      <c r="Z41" s="0" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="AD41" t="inlineStr">
+      <c r="AB41" s="0" t="inlineStr">
+        <is>
+          <t>₹1,00,000 per month (Salaried), ₹12 Lakhs ITR per annum (Self-employed) (est)</t>
+        </is>
+      </c>
+      <c r="AC41" s="0" t="inlineStr">
+        <is>
+          <t>Salaried, Self-Employed</t>
+        </is>
+      </c>
+      <c r="AD41" s="0" t="inlineStr">
         <is>
           <t>21 - 60</t>
         </is>
       </c>
+      <c r="AF41" s="0" t="inlineStr">
+        <is>
+          <t>750+ (est)</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="0" t="inlineStr">
         <is>
           <t>HDFC Bank</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="0" t="inlineStr">
         <is>
           <t>Shoppers Stop HDFC Bank Credit Card</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="0" t="inlineStr">
         <is>
           <t>928ad20cce77</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D42" s="0" t="inlineStr">
         <is>
           <t>credit</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E42" s="0" t="inlineStr">
         <is>
           <t>RuPay</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F42" s="0" t="inlineStr">
         <is>
           <t>null</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G42" s="0" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="H42" s="0" t="inlineStr">
         <is>
           <t>https://www.hdfcbank.com/credit-cards/shoppers-stop-credit-card</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="I42" s="0" t="inlineStr">
         <is>
           <t>2026-06-06T16:23:37.901890+00:00</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="K42" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="L42" s="0" t="inlineStr">
         <is>
           <t>299</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr">
+      <c r="R42" s="0" t="inlineStr">
         <is>
           <t>points</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr">
+      <c r="S42" s="0" t="inlineStr">
         <is>
           <t>3% Reward Points on every Shopper Stop purchase</t>
         </is>
       </c>
-      <c r="T42" t="inlineStr">
+      <c r="T42" s="0" t="inlineStr">
         <is>
           <t>Shoppers Stop: 3% Reward Points</t>
         </is>
       </c>
-      <c r="U42" t="inlineStr">
+      <c r="U42" s="0" t="inlineStr">
         <is>
           <t>Welcome: ₹500 Welcome Voucher, Complimentary Shoppers Stop Silver Edge membership | Milestone: Reward Points worth ₹500 per month for a purchase of ₹15,000 or above on weekends at Shoppers Stop</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr">
+      <c r="V42" s="0" t="inlineStr">
         <is>
           <t>1% fuel surcharge waiver</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
+      <c r="Z42" s="0" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
+      <c r="AB42" s="0" t="inlineStr">
         <is>
           <t>20000</t>
         </is>
       </c>
-      <c r="AD42" t="inlineStr">
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Salaried and Self-Employed (est)</t>
+        </is>
+      </c>
+      <c r="AD42" s="0" t="inlineStr">
         <is>
           <t>21 - 65 (for self-employed)</t>
         </is>
       </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>720+ (est)</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="0" t="inlineStr">
         <is>
           <t>HDFC Bank</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="0" t="inlineStr">
         <is>
           <t>Solitaire Credit Card</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="0" t="inlineStr">
         <is>
           <t>d13a38a7ddae</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D43" s="0" t="inlineStr">
         <is>
           <t>credit</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G43" s="0" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H43" s="0" t="inlineStr">
         <is>
           <t>https://www.hdfcbank.com/credit-cards/solitaire-credit-card</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="I43" s="0" t="inlineStr">
         <is>
           <t>2026-06-06T16:24:26.540143+00:00</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="L43" s="0" t="inlineStr">
         <is>
           <t>500+GST</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr">
+      <c r="R43" s="0" t="inlineStr">
         <is>
           <t>points/cashback</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr">
+      <c r="S43" s="0" t="inlineStr">
         <is>
           <t>3 Reward Points for every ₹200 spent</t>
         </is>
       </c>
-      <c r="T43" t="inlineStr">
+      <c r="T43" s="0" t="inlineStr">
         <is>
           <t>dining and grocery expenses: 50% more Reward Points</t>
         </is>
       </c>
-      <c r="U43" t="inlineStr">
+      <c r="U43" s="0" t="inlineStr">
         <is>
           <t>Milestone: ₹1,000 Gift Voucher on crossing spends of ₹75,000 in 6 months; Up to 2 vouchers in a year</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr">
+      <c r="V43" s="0" t="inlineStr">
         <is>
           <t>1% fuel surcharge waiver on transactions ₹400-₹5,000. Max waiver: ₹250 per statement cycle</t>
         </is>
       </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>Rs. 10,000 per month (est)</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Salaried and Self-Employed (est)</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>720+ (est)</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="0" t="inlineStr">
         <is>
           <t>HDFC Bank</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="0" t="inlineStr">
         <is>
           <t>Superia Credit Card</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="0" t="inlineStr">
         <is>
           <t>78f7ce9b4e48</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D44" s="0" t="inlineStr">
         <is>
           <t>credit</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G44" s="0" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="H44" s="0" t="inlineStr">
         <is>
           <t>https://www.hdfcbank.com/credit-cards/superia-credit-card</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="I44" s="0" t="inlineStr">
         <is>
           <t>2026-06-06T16:25:17.875819+00:00</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>1000 (est)</t>
+        </is>
+      </c>
+      <c r="L44" s="0" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="N44" s="0" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr">
+      <c r="R44" s="0" t="inlineStr">
         <is>
           <t>points</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr">
+      <c r="S44" s="0" t="inlineStr">
         <is>
           <t>3 Reward Points for every ₹200 spent</t>
         </is>
       </c>
-      <c r="T44" t="inlineStr">
+      <c r="T44" s="0" t="inlineStr">
         <is>
           <t>Dining expenses at select premium restaurants: 50% more Reward Points</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr">
+      <c r="U44" s="0" t="inlineStr">
         <is>
           <t>Welcome: 1000 Reward Points as welcome benefit</t>
         </is>
       </c>
-      <c r="V44" t="inlineStr">
+      <c r="V44" s="0" t="inlineStr">
         <is>
           <t>Get a 1% fuel surcharge waiver on a minimum transaction of ₹400. Max waiver: ₹500/cycle.</t>
         </is>
       </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>Rs. 75,000 per month (est)</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Salaried and Self-Employed (est)</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>750+ (est)</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="0" t="inlineStr">
         <is>
           <t>HDFC Bank</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="0" t="inlineStr">
         <is>
           <t>Swiggy BLCK HDFC Bank Credit Card</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="0" t="inlineStr">
         <is>
           <t>60b6e05e7867</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D45" s="0" t="inlineStr">
         <is>
           <t>credit</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E45" s="0" t="inlineStr">
         <is>
           <t>Mastercard</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G45" s="0" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="H45" s="0" t="inlineStr">
         <is>
           <t>https://www.hdfc.bank.in/credit-cards/swiggy-blck-hdfc-bank-credit-card</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="I45" s="0" t="inlineStr">
         <is>
           <t>2026-06-06T16:26:11.856133+00:00</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="K45" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="L45" s="0" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr">
+      <c r="R45" s="0" t="inlineStr">
         <is>
           <t>CashBack</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr">
+      <c r="S45" s="0" t="inlineStr">
         <is>
           <t>10% CashBack on Swiggy app transactions, 5% CashBack on select online merchants and categories, 1% CashBack on all other categories.</t>
         </is>
       </c>
-      <c r="U45" t="inlineStr">
+      <c r="U45" s="0" t="inlineStr">
         <is>
           <t>Welcome: Complimentary Swiggy BLCK membership for 3 months</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
+      <c r="Z45" s="0" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
+      <c r="AB45" s="0" t="inlineStr">
         <is>
           <t>10000000000</t>
         </is>
       </c>
-      <c r="AD45" t="inlineStr">
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Salaried and Self-Employed (est)</t>
+        </is>
+      </c>
+      <c r="AD45" s="0" t="inlineStr">
         <is>
           <t>Min 21 years - Max 65 years for self-employed individuals</t>
         </is>
       </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>720+ (est)</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="0" t="inlineStr">
         <is>
           <t>HDFC Bank</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="0" t="inlineStr">
         <is>
           <t>Swiggy HDFC Bank Credit Card</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="0" t="inlineStr">
         <is>
           <t>5aaaa512604d</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D46" s="0" t="inlineStr">
         <is>
           <t>credit</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E46" s="0" t="inlineStr">
         <is>
           <t>Visa</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G46" s="0" t="inlineStr">
         <is>
           <t>cashback</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="H46" s="0" t="inlineStr">
         <is>
           <t>https://www.hdfc.bank.in/credit-cards/swiggy-hdfc-bank-credit-card</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="I46" s="0" t="inlineStr">
         <is>
           <t>2026-06-06T16:27:04.624385+00:00</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="K46" s="0" t="inlineStr">
         <is>
           <t>500</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr">
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="R46" s="0" t="inlineStr">
         <is>
           <t>cashback</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr">
+      <c r="S46" s="0" t="inlineStr">
         <is>
           <t>10% cashback on Swiggy food order, 5% Cashback on online spends, 1% Cashback on all other categories</t>
         </is>
       </c>
-      <c r="T46" t="inlineStr">
+      <c r="T46" s="0" t="inlineStr">
         <is>
           <t>Swiggy food order: 10%; online spends: 5%; all other categories: 1%</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr">
+      <c r="U46" s="0" t="inlineStr">
         <is>
           <t>Welcome: Complimentary 3 Months Swiggy One Membership</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
+      <c r="Z46" s="0" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
+      <c r="AB46" s="0" t="inlineStr">
         <is>
           <t>15000</t>
         </is>
       </c>
-      <c r="AD46" t="inlineStr">
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Salaried and Self-Employed</t>
+        </is>
+      </c>
+      <c r="AD46" s="0" t="inlineStr">
         <is>
           <t>21 years - 60 years for salaried individuals, 65 years for self-employed individuals</t>
         </is>
       </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>720+ (est)</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="0" t="inlineStr">
         <is>
           <t>HDFC Bank</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="0" t="inlineStr">
         <is>
           <t>Swiggy Ornge HDFC Bank Credit Card</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="0" t="inlineStr">
         <is>
           <t>f852f77c3e74</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D47" s="0" t="inlineStr">
         <is>
           <t>credit</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E47" s="0" t="inlineStr">
         <is>
           <t>Mastercard</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F47" s="0" t="inlineStr">
         <is>
           <t>null</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G47" s="0" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="H47" s="0" t="inlineStr">
         <is>
           <t>https://www.hdfc.bank.in/credit-cards/swiggy-ornge-hdfc-bank-credit-card</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="I47" s="0" t="inlineStr">
         <is>
           <t>2026-06-06T16:27:58.190841+00:00</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="K47" s="0" t="inlineStr">
         <is>
           <t>500</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="L47" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="M47" s="0" t="inlineStr">
         <is>
           <t>null</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="N47" s="0" t="inlineStr">
         <is>
           <t>null</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
+      <c r="P47" s="0" t="inlineStr">
         <is>
           <t>null</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr">
+      <c r="R47" s="0" t="inlineStr">
         <is>
           <t>cashback</t>
         </is>
       </c>
-      <c r="S47" t="inlineStr">
+      <c r="S47" s="0" t="inlineStr">
         <is>
           <t>5% Cashback across Swiggy and select online spends, 1% CashBack on other spends</t>
         </is>
       </c>
-      <c r="T47" t="inlineStr">
+      <c r="T47" s="0" t="inlineStr">
         <is>
           <t>Swiggy app spends (Food orders, Instamart, and Dineout): 5%; Online spends across online Merchants: 5%; Other categories: 1%</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr">
+      <c r="U47" s="0" t="inlineStr">
         <is>
           <t>Welcome: Complimentary Swiggy One Membership for 12 months | Milestone: null</t>
         </is>
       </c>
-      <c r="V47" t="inlineStr">
+      <c r="V47" s="0" t="inlineStr">
         <is>
           <t>null</t>
         </is>
       </c>
-      <c r="W47" t="inlineStr">
+      <c r="W47" s="0" t="inlineStr">
         <is>
           <t>null</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
+      <c r="X47" s="0" t="inlineStr">
         <is>
           <t>null</t>
         </is>
       </c>
-      <c r="Y47" t="inlineStr">
+      <c r="Y47" s="0" t="inlineStr">
         <is>
           <t>Movie: null | Dining: null | Travel: null | Insurance: null</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
+      <c r="Z47" s="0" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
+      <c r="AB47" s="0" t="inlineStr">
         <is>
           <t>2000000000</t>
         </is>
       </c>
-      <c r="AD47" t="inlineStr">
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Salaried and Self-Employed (est)</t>
+        </is>
+      </c>
+      <c r="AD47" s="0" t="inlineStr">
         <is>
           <t>Min 21 years - Max 65 years for self-employed individuals</t>
         </is>
       </c>
-      <c r="AF47" t="inlineStr">
+      <c r="AF47" s="0" t="inlineStr">
         <is>
           <t>null</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="0" t="inlineStr">
         <is>
           <t>HDFC Bank</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="0" t="inlineStr">
         <is>
           <t>Tata Neu Infinity Credit Card</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="0" t="inlineStr">
         <is>
           <t>91537baf0db9</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D48" s="0" t="inlineStr">
         <is>
           <t>credit</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E48" s="0" t="inlineStr">
         <is>
           <t>RuPay</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F48" s="0" t="inlineStr">
         <is>
           <t>infinity</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G48" s="0" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="H48" s="0" t="inlineStr">
         <is>
           <t>https://www.hdfcbank.com/credit-cards/tata-neu-infinity-hdfc-bank-credit-card</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="I48" s="0" t="inlineStr">
         <is>
           <t>2026-06-06T16:28:57.769648+00:00</t>
         </is>
       </c>
-      <c r="R48" t="inlineStr">
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>1499</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>1499</t>
+        </is>
+      </c>
+      <c r="R48" s="0" t="inlineStr">
         <is>
           <t>NeuCoins</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr">
+      <c r="S48" s="0" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="W48" t="inlineStr">
+      <c r="W48" s="0" t="inlineStr">
         <is>
           <t>2 per calendar quarter (up to 8 per calendar year)</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
+      <c r="X48" s="0" t="inlineStr">
         <is>
           <t>4 per calendar year</t>
         </is>
       </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>Rs. 1,00,000 per month</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Salaried and Self-Employed</t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>730+ (est)</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="0" t="inlineStr">
         <is>
           <t>HDFC Bank</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="0" t="inlineStr">
         <is>
           <t>Tata Neu Plus Credit Card</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="0" t="inlineStr">
         <is>
           <t>ea2c8d95689f</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D49" s="0" t="inlineStr">
         <is>
           <t>credit</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E49" s="0" t="inlineStr">
         <is>
           <t>RuPay</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G49" s="0" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="H49" s="0" t="inlineStr">
         <is>
           <t>https://www.hdfc.bank.in/credit-cards/tata-neu-plus-hdfc-bank-credit-card</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="I49" s="0" t="inlineStr">
         <is>
           <t>2026-06-06T16:30:02.442418+00:00</t>
         </is>
       </c>
-      <c r="R49" t="inlineStr">
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R49" s="0" t="inlineStr">
         <is>
           <t>NeuCoins</t>
         </is>
       </c>
-      <c r="S49" t="inlineStr">
+      <c r="S49" s="0" t="inlineStr">
         <is>
           <t>2% on Tata Neu and partner Tata Brands, 1% on other Non-UPI spends</t>
         </is>
       </c>
-      <c r="W49" t="inlineStr">
+      <c r="W49" s="0" t="inlineStr">
         <is>
           <t>1 per calendar quarter (up to 4 per calendar year)</t>
         </is>
       </c>
-      <c r="AD49" t="inlineStr">
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>Rs. 25,000 per month</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Salaried and Self-Employed</t>
+        </is>
+      </c>
+      <c r="AD49" s="0" t="inlineStr">
         <is>
           <t>21 - 60 for Salaried, 65 for Self-Employed</t>
         </is>
       </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>720+ (est)</t>
+        </is>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="0" t="inlineStr">
         <is>
           <t>HDFC Bank</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="0" t="inlineStr">
         <is>
           <t>Teachers Platinum Credit Card</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="0" t="inlineStr">
         <is>
           <t>c9fe016da221</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D50" s="0" t="inlineStr">
         <is>
           <t>credit</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F50" s="0" t="inlineStr">
         <is>
           <t>platinum</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G50" s="0" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="H50" s="0" t="inlineStr">
         <is>
           <t>https://www.hdfcbank.com/credit-cards/teachers-platinum-credit-card</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="I50" s="0" t="inlineStr">
         <is>
           <t>2026-06-06T16:30:51.769183+00:00</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Rs. 500 (est)</t>
+        </is>
+      </c>
+      <c r="L50" s="0" t="inlineStr">
         <is>
           <t>500</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr">
+      <c r="R50" s="0" t="inlineStr">
         <is>
           <t>points/cashback</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr">
+      <c r="S50" s="0" t="inlineStr">
         <is>
           <t>500 Reward Points on Teacher's Day (05th September) every year. Up to 3X Reward Points on spends of ₹200 with an annual capping of 2,400 Reward Points.</t>
         </is>
       </c>
-      <c r="V50" t="inlineStr">
+      <c r="V50" s="0" t="inlineStr">
         <is>
           <t>Get a 1% fuel surcharge waiver on transactions from ₹400 to ₹5,000. Max waiver: ₹250/cycle.</t>
         </is>
       </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>Rs. 20,000 per month (est)</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Salaried (primarily Teachers) (est)</t>
+        </is>
+      </c>
+      <c r="AD50" t="inlineStr">
+        <is>
+          <t>21 to 60 years (est)</t>
+        </is>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>750 and above (est)</t>
+        </is>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="0" t="inlineStr">
         <is>
           <t>HDFC Bank</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="0" t="inlineStr">
         <is>
           <t>Titanium Edge Credit Card</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="0" t="inlineStr">
         <is>
           <t>009e40238441</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D51" s="0" t="inlineStr">
         <is>
           <t>credit</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G51" s="0" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="H51" s="0" t="inlineStr">
         <is>
           <t>https://www.hdfcbank.com/credit-cards/titanium-edge-credit-card</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="I51" s="0" t="inlineStr">
         <is>
           <t>2026-06-06T16:31:39.142215+00:00</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Rs. 500 (est)</t>
+        </is>
+      </c>
+      <c r="L51" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
+      <c r="N51" s="0" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr">
+      <c r="R51" s="0" t="inlineStr">
         <is>
           <t>points/cashback</t>
         </is>
       </c>
-      <c r="S51" t="inlineStr">
+      <c r="S51" s="0" t="inlineStr">
         <is>
           <t>2 Reward Points for every ₹ 200 spent</t>
         </is>
       </c>
-      <c r="T51" t="inlineStr">
+      <c r="T51" s="0" t="inlineStr">
         <is>
           <t>Dining expenses: 50% more Reward Points</t>
         </is>
       </c>
-      <c r="V51" t="inlineStr">
+      <c r="V51" s="0" t="inlineStr">
         <is>
           <t>100% fuel surcharge waiver (Maximum waiver of ₹250 per statement cycle)</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
+      <c r="Z51" s="0" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>Rs. 20,000 per month (est)</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Salaried &amp; Self-Employed (est)</t>
+        </is>
+      </c>
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t>21 to 65 years (est)</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>750 and above (est)</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="0" t="inlineStr">
         <is>
           <t>HDFC Bank</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="0" t="inlineStr">
         <is>
           <t>Travel Credit Card</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="0" t="inlineStr">
         <is>
           <t>8bd5636e2d3b</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D52" s="0" t="inlineStr">
         <is>
           <t>credit</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="G52" s="0" t="inlineStr">
         <is>
           <t>travel</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="H52" s="0" t="inlineStr">
         <is>
           <t>https://www.hdfcbank.com/credit-cards/travel-credit-card</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="I52" s="0" t="inlineStr">
         <is>
           <t>2026-06-06T16:33:03.368252+00:00</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr">
+      <c r="K52" s="0" t="inlineStr">
+        <is>
+          <t>1000 (est)</t>
+        </is>
+      </c>
+      <c r="L52" s="0" t="inlineStr">
+        <is>
+          <t>1000 (est)</t>
+        </is>
+      </c>
+      <c r="R52" s="0" t="inlineStr">
         <is>
           <t>points/cashback/miles</t>
         </is>
       </c>
-      <c r="AD52" t="inlineStr">
+      <c r="S52" s="0" t="inlineStr">
+        <is>
+          <t>1.33% (est)</t>
+        </is>
+      </c>
+      <c r="AB52" s="0" t="inlineStr">
+        <is>
+          <t>70000 per month (est)</t>
+        </is>
+      </c>
+      <c r="AC52" s="0" t="inlineStr">
+        <is>
+          <t>Salaried / Self-employed (est)</t>
+        </is>
+      </c>
+      <c r="AD52" s="0" t="inlineStr">
         <is>
           <t>21 - ?</t>
         </is>
       </c>
+      <c r="AF52" s="0" t="inlineStr">
+        <is>
+          <t>750+ (est)</t>
+        </is>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="0" t="inlineStr">
         <is>
           <t>HDFC Bank</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="0" t="inlineStr">
         <is>
           <t>Visa Signature Credit Card</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="0" t="inlineStr">
         <is>
           <t>ea37d56a67da</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D53" s="0" t="inlineStr">
         <is>
           <t>credit</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E53" s="0" t="inlineStr">
         <is>
           <t>Visa</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F53" s="0" t="inlineStr">
         <is>
           <t>signature</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G53" s="0" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="H53" s="0" t="inlineStr">
         <is>
           <t>https://www.hdfcbank.com/credit-cards/visa-signature-credit-card</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="I53" s="0" t="inlineStr">
         <is>
           <t>2026-06-06T16:33:47.356799+00:00</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="K53" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="L53" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr">
+      <c r="N53" s="0" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
       </c>
-      <c r="R53" t="inlineStr">
+      <c r="R53" s="0" t="inlineStr">
         <is>
           <t>points</t>
         </is>
       </c>
-      <c r="S53" t="inlineStr">
+      <c r="S53" s="0" t="inlineStr">
         <is>
           <t>2 Reward Points for every ₹200 spent</t>
         </is>
       </c>
-      <c r="V53" t="inlineStr">
+      <c r="V53" s="0" t="inlineStr">
         <is>
           <t>up to ₹6,000 spent monthly on fuel annually</t>
         </is>
       </c>
-      <c r="W53" t="inlineStr">
+      <c r="W53" s="0" t="inlineStr">
         <is>
           <t>Priority Pass lounge access up to ₹8,300 yearly savings</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
+      <c r="Z53" s="0" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="AB53" s="0" t="inlineStr">
+        <is>
+          <t>35000 per month (est)</t>
+        </is>
+      </c>
+      <c r="AC53" s="0" t="inlineStr">
+        <is>
+          <t>Salaried / Self-employed (est)</t>
+        </is>
+      </c>
+      <c r="AD53" t="inlineStr">
+        <is>
+          <t>21 to 60 years for salaried, 21 to 65 years for self-employed (est)</t>
+        </is>
+      </c>
+      <c r="AF53" s="0" t="inlineStr">
+        <is>
+          <t>700-750+ (est)</t>
+        </is>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="0" t="inlineStr">
         <is>
           <t>HDFC Bank</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="0" t="inlineStr">
         <is>
           <t>World MasterCard Credit Card</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C54" s="0" t="inlineStr">
         <is>
           <t>0c715afd2a8e</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D54" s="0" t="inlineStr">
         <is>
           <t>credit</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E54" s="0" t="inlineStr">
         <is>
           <t>Mastercard</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G54" s="0" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="H54" s="0" t="inlineStr">
         <is>
           <t>https://www.hdfcbank.com/credit-cards/world-mastercard-credit-card</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="I54" s="0" t="inlineStr">
         <is>
           <t>2026-06-06T16:34:33.312216+00:00</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="K54" s="0" t="inlineStr">
+        <is>
+          <t>2500 (est)</t>
+        </is>
+      </c>
+      <c r="L54" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr">
+      <c r="N54" s="0" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
       </c>
-      <c r="R54" t="inlineStr">
+      <c r="R54" s="0" t="inlineStr">
         <is>
           <t>points</t>
         </is>
       </c>
-      <c r="S54" t="inlineStr">
+      <c r="S54" s="0" t="inlineStr">
         <is>
           <t>2 Reward Points for every ₹200 spent</t>
         </is>
       </c>
-      <c r="V54" t="inlineStr">
+      <c r="V54" s="0" t="inlineStr">
         <is>
           <t>up to ₹6,000 spent monthly on fuel annually</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
+      <c r="Z54" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="AB54" s="0" t="inlineStr">
+        <is>
+          <t>70000 per month (est)</t>
+        </is>
+      </c>
+      <c r="AC54" s="0" t="inlineStr">
+        <is>
+          <t>Salaried / Self-employed (est)</t>
+        </is>
+      </c>
+      <c r="AD54" t="inlineStr">
+        <is>
+          <t>21 to 60 years for salaried, 21 to 65 years for self-employed (est)</t>
+        </is>
+      </c>
+      <c r="AF54" s="0" t="inlineStr">
+        <is>
+          <t>750+ (est)</t>
         </is>
       </c>
     </row>
@@ -4504,7 +5653,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D17"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1" outlineLevelCol="0"/>
   <cols>
     <col width="19.63" customWidth="1" style="3" min="2" max="2"/>
   </cols>
@@ -4540,10 +5689,10 @@
           <t>HDFC Bank</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="0" t="n">
         <v>53</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="0" t="inlineStr">
         <is>
           <t>✅ Done</t>
         </is>
